--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/71.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/71.xlsx
@@ -426,13 +426,13 @@
         <v>-5.516321111632704</v>
       </c>
       <c r="E2">
-        <v>-10.23020527649186</v>
+        <v>-13.06134560634436</v>
       </c>
       <c r="F2">
-        <v>-3.937335615413713</v>
+        <v>-4.130769344376231</v>
       </c>
       <c r="G2">
-        <v>-8.423924551066916</v>
+        <v>-7.420321695935581</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.872931872302133</v>
       </c>
       <c r="E3">
-        <v>-11.25677528570635</v>
+        <v>-13.36369939079187</v>
       </c>
       <c r="F3">
-        <v>-3.882617806621792</v>
+        <v>-4.087490461049569</v>
       </c>
       <c r="G3">
-        <v>-8.269153084844243</v>
+        <v>-7.424404900476081</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.188183172282717</v>
       </c>
       <c r="E4">
-        <v>-11.44479531559267</v>
+        <v>-13.99646605539745</v>
       </c>
       <c r="F4">
-        <v>-3.628801064199607</v>
+        <v>-4.069384006359177</v>
       </c>
       <c r="G4">
-        <v>-7.413311846708441</v>
+        <v>-7.298668830223475</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.569824297030783</v>
       </c>
       <c r="E5">
-        <v>-13.14563087697043</v>
+        <v>-14.03126581308819</v>
       </c>
       <c r="F5">
-        <v>-3.505848975704285</v>
+        <v>-4.027246613313572</v>
       </c>
       <c r="G5">
-        <v>-7.640257347152441</v>
+        <v>-7.073134437230971</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.023672826381795</v>
       </c>
       <c r="E6">
-        <v>-14.5384310608083</v>
+        <v>-15.05969646097621</v>
       </c>
       <c r="F6">
-        <v>-3.458804334164495</v>
+        <v>-3.682496667616474</v>
       </c>
       <c r="G6">
-        <v>-7.597147427091683</v>
+        <v>-7.242989480328801</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.582420461359653</v>
       </c>
       <c r="E7">
-        <v>-14.38633215567043</v>
+        <v>-15.91723076927018</v>
       </c>
       <c r="F7">
-        <v>-3.642513029818147</v>
+        <v>-3.919365841344784</v>
       </c>
       <c r="G7">
-        <v>-7.786200580540266</v>
+        <v>-6.972273541442492</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.240466625977701</v>
       </c>
       <c r="E8">
-        <v>-14.3319790790624</v>
+        <v>-17.10094583538221</v>
       </c>
       <c r="F8">
-        <v>-3.432642834849281</v>
+        <v>-3.468749713202506</v>
       </c>
       <c r="G8">
-        <v>-7.524819358939481</v>
+        <v>-7.184041478206055</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.99678775542803</v>
       </c>
       <c r="E9">
-        <v>-16.62755450215561</v>
+        <v>-17.51958953692493</v>
       </c>
       <c r="F9">
-        <v>-3.451409498359704</v>
+        <v>-3.506978040474301</v>
       </c>
       <c r="G9">
-        <v>-7.267086652904777</v>
+        <v>-6.553867781036903</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.826879368553308</v>
       </c>
       <c r="E10">
-        <v>-15.4069423066338</v>
+        <v>-18.27616343112365</v>
       </c>
       <c r="F10">
-        <v>-2.926337222951598</v>
+        <v>-3.055080427959892</v>
       </c>
       <c r="G10">
-        <v>-7.609558906877836</v>
+        <v>-6.521076828972521</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.710086721152484</v>
       </c>
       <c r="E11">
-        <v>-16.80914951412241</v>
+        <v>-19.24185151552748</v>
       </c>
       <c r="F11">
-        <v>-2.845697313023872</v>
+        <v>-3.084557881988512</v>
       </c>
       <c r="G11">
-        <v>-5.792987155913665</v>
+        <v>-6.147064169594223</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.63229339482751</v>
       </c>
       <c r="E12">
-        <v>-18.12232433044067</v>
+        <v>-20.16469507190438</v>
       </c>
       <c r="F12">
-        <v>-2.532183445351537</v>
+        <v>-2.87436628046736</v>
       </c>
       <c r="G12">
-        <v>-6.414829967092574</v>
+        <v>-5.280328294279705</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.584028048353873</v>
       </c>
       <c r="E13">
-        <v>-18.10619741086636</v>
+        <v>-20.31895364693116</v>
       </c>
       <c r="F13">
-        <v>-2.249103796058057</v>
+        <v>-2.804741171894658</v>
       </c>
       <c r="G13">
-        <v>-5.799111962724417</v>
+        <v>-5.066602299072807</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.570058262499261</v>
       </c>
       <c r="E14">
-        <v>-19.24411086248818</v>
+        <v>-21.60541500800813</v>
       </c>
       <c r="F14">
-        <v>-2.542116398878506</v>
+        <v>-2.43381315953429</v>
       </c>
       <c r="G14">
-        <v>-6.003405337723622</v>
+        <v>-4.65896586010556</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.590284831500639</v>
       </c>
       <c r="E15">
-        <v>-20.69011783660844</v>
+        <v>-23.38405683034523</v>
       </c>
       <c r="F15">
-        <v>-2.045868823985615</v>
+        <v>-2.381376674569679</v>
       </c>
       <c r="G15">
-        <v>-4.920087312619529</v>
+        <v>-4.354088328244533</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.63844553353607</v>
       </c>
       <c r="E16">
-        <v>-20.22536518293748</v>
+        <v>-24.33840249462095</v>
       </c>
       <c r="F16">
-        <v>-2.03638981579538</v>
+        <v>-2.04345578974126</v>
       </c>
       <c r="G16">
-        <v>-4.473535114777148</v>
+        <v>-4.045759392034054</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.701110923811491</v>
       </c>
       <c r="E17">
-        <v>-23.22660858902098</v>
+        <v>-25.44839390650595</v>
       </c>
       <c r="F17">
-        <v>-1.780778001211328</v>
+        <v>-1.585184718429712</v>
       </c>
       <c r="G17">
-        <v>-4.053774377928772</v>
+        <v>-3.443781736448926</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.754441184838153</v>
       </c>
       <c r="E18">
-        <v>-23.11813916885043</v>
+        <v>-25.63971158618418</v>
       </c>
       <c r="F18">
-        <v>-1.33017347021269</v>
+        <v>-1.460623940438153</v>
       </c>
       <c r="G18">
-        <v>-3.904948882512359</v>
+        <v>-3.565771388213285</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.77658782763213</v>
       </c>
       <c r="E19">
-        <v>-24.91474363016741</v>
+        <v>-26.66787642854741</v>
       </c>
       <c r="F19">
-        <v>-1.035388161150249</v>
+        <v>-1.283879329539836</v>
       </c>
       <c r="G19">
-        <v>-2.662393712562493</v>
+        <v>-2.874694241222643</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.747891641235849</v>
       </c>
       <c r="E20">
-        <v>-22.91708220861548</v>
+        <v>-27.4443525114147</v>
       </c>
       <c r="F20">
-        <v>-1.231303678851555</v>
+        <v>-0.6549272967184641</v>
       </c>
       <c r="G20">
-        <v>-3.895652021023404</v>
+        <v>-2.883401074434006</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.657207898295772</v>
       </c>
       <c r="E21">
-        <v>-25.69420171876593</v>
+        <v>-28.73160505924905</v>
       </c>
       <c r="F21">
-        <v>-0.5710741496352785</v>
+        <v>-0.4989747076304152</v>
       </c>
       <c r="G21">
-        <v>-3.57030886231264</v>
+        <v>-2.310650704546391</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.505225980878557</v>
       </c>
       <c r="E22">
-        <v>-24.65557493707546</v>
+        <v>-29.058979865323</v>
       </c>
       <c r="F22">
-        <v>-0.5239135366590971</v>
+        <v>-0.3005848564969476</v>
       </c>
       <c r="G22">
-        <v>-2.143737970602746</v>
+        <v>-2.125666396543059</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.302107810130445</v>
       </c>
       <c r="E23">
-        <v>-25.93915396949299</v>
+        <v>-29.21046824839612</v>
       </c>
       <c r="F23">
-        <v>-0.3565187086361786</v>
+        <v>-0.535378969881245</v>
       </c>
       <c r="G23">
-        <v>-2.812785654733574</v>
+        <v>-1.946308243133577</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.068108737807276</v>
       </c>
       <c r="E24">
-        <v>-28.10444522993199</v>
+        <v>-29.53079920806315</v>
       </c>
       <c r="F24">
-        <v>-0.4342402802038422</v>
+        <v>0.2451038268320324</v>
       </c>
       <c r="G24">
-        <v>-2.294926189874116</v>
+        <v>-1.588338609267669</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.8251045709143895</v>
       </c>
       <c r="E25">
-        <v>-27.28949587395715</v>
+        <v>-30.05099100310359</v>
       </c>
       <c r="F25">
-        <v>-0.02632152147146204</v>
+        <v>-0.3267206764226748</v>
       </c>
       <c r="G25">
-        <v>-1.67611706391008</v>
+        <v>-1.306850738198426</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.5924551110937503</v>
       </c>
       <c r="E26">
-        <v>-26.06853480868405</v>
+        <v>-29.68577421204347</v>
       </c>
       <c r="F26">
-        <v>-0.2389857996899707</v>
+        <v>-0.04948681589075022</v>
       </c>
       <c r="G26">
-        <v>-1.294441869156865</v>
+        <v>-0.9593710760996121</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.387050340417394</v>
       </c>
       <c r="E27">
-        <v>-25.98112216993038</v>
+        <v>-30.20104029845266</v>
       </c>
       <c r="F27">
-        <v>-0.06924669191712962</v>
+        <v>0.1264087184196968</v>
       </c>
       <c r="G27">
-        <v>-2.016866226453004</v>
+        <v>-0.9019738562639866</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.2195674137267652</v>
       </c>
       <c r="E28">
-        <v>-25.99783884551282</v>
+        <v>-29.64102751322977</v>
       </c>
       <c r="F28">
-        <v>-0.2592758308541418</v>
+        <v>-0.1301888533736865</v>
       </c>
       <c r="G28">
-        <v>-1.3982241881428</v>
+        <v>-1.037320077356481</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.09662632482798275</v>
       </c>
       <c r="E29">
-        <v>-26.46445213785731</v>
+        <v>-30.36246731622609</v>
       </c>
       <c r="F29">
-        <v>-0.1432480654788207</v>
+        <v>-0.6182629271031551</v>
       </c>
       <c r="G29">
-        <v>-1.815165320832774</v>
+        <v>-0.7898449868202621</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.01843231056194135</v>
       </c>
       <c r="E30">
-        <v>-26.61397189876246</v>
+        <v>-29.78252534646101</v>
       </c>
       <c r="F30">
-        <v>-0.6102990028926407</v>
+        <v>-0.3146024896871208</v>
       </c>
       <c r="G30">
-        <v>-2.020970316950234</v>
+        <v>-0.6555430635642124</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.02068286394472205</v>
       </c>
       <c r="E31">
-        <v>-25.95432565046259</v>
+        <v>-29.07362408845434</v>
       </c>
       <c r="F31">
-        <v>-0.5344089516525669</v>
+        <v>-0.5692741072689952</v>
       </c>
       <c r="G31">
-        <v>-0.8563667590018286</v>
+        <v>-0.4054285102463774</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.0289021272855205</v>
       </c>
       <c r="E32">
-        <v>-26.03980289273889</v>
+        <v>-29.00435682997885</v>
       </c>
       <c r="F32">
-        <v>-0.3918303542827159</v>
+        <v>-0.6411208972160047</v>
       </c>
       <c r="G32">
-        <v>-0.9927807746320889</v>
+        <v>-0.6252375403505694</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.01840860652122754</v>
       </c>
       <c r="E33">
-        <v>-24.74900142582748</v>
+        <v>-29.29945080103057</v>
       </c>
       <c r="F33">
-        <v>-0.641904532779053</v>
+        <v>-0.6978508104293261</v>
       </c>
       <c r="G33">
-        <v>-1.659481399375506</v>
+        <v>-0.2975447115078032</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.0005321574115664516</v>
       </c>
       <c r="E34">
-        <v>-24.21906827362465</v>
+        <v>-28.27718144214293</v>
       </c>
       <c r="F34">
-        <v>-0.6693243221791195</v>
+        <v>-0.8885451283907863</v>
       </c>
       <c r="G34">
-        <v>-1.282254913405548</v>
+        <v>0.001343772261210265</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.01505155625749046</v>
       </c>
       <c r="E35">
-        <v>-25.26925759564345</v>
+        <v>-27.64337855131181</v>
       </c>
       <c r="F35">
-        <v>-0.8483527420069542</v>
+        <v>-0.9397498310274349</v>
       </c>
       <c r="G35">
-        <v>-1.625178826192869</v>
+        <v>-0.5410201413304371</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.0215997462858887</v>
       </c>
       <c r="E36">
-        <v>-24.69867281099321</v>
+        <v>-26.72233333543856</v>
       </c>
       <c r="F36">
-        <v>-0.166805177679633</v>
+        <v>-0.8465096245357253</v>
       </c>
       <c r="G36">
-        <v>-2.266095737354452</v>
+        <v>-0.2243942588094</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.0185962532996772</v>
       </c>
       <c r="E37">
-        <v>-23.07870027410986</v>
+        <v>-25.97831875228612</v>
       </c>
       <c r="F37">
-        <v>-0.3376882608357402</v>
+        <v>-0.8559687519082929</v>
       </c>
       <c r="G37">
-        <v>-1.926714604977271</v>
+        <v>-0.2421055501155125</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.009472747884347594</v>
       </c>
       <c r="E38">
-        <v>-23.77646884916032</v>
+        <v>-25.65252008990995</v>
       </c>
       <c r="F38">
-        <v>-0.6451285387107487</v>
+        <v>-0.7924437408898072</v>
       </c>
       <c r="G38">
-        <v>-2.4123548708378</v>
+        <v>0.06894117121431546</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.002494162341343188</v>
       </c>
       <c r="E39">
-        <v>-22.25638104463911</v>
+        <v>-24.85423964758731</v>
       </c>
       <c r="F39">
-        <v>-0.3198849886147732</v>
+        <v>-0.8767533184119353</v>
       </c>
       <c r="G39">
-        <v>-1.156957448244248</v>
+        <v>0.2168972886818876</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.00773584532778544</v>
       </c>
       <c r="E40">
-        <v>-22.50361756159482</v>
+        <v>-24.02631773603936</v>
       </c>
       <c r="F40">
-        <v>-0.7617212506547791</v>
+        <v>-0.7899478699051723</v>
       </c>
       <c r="G40">
-        <v>-1.641905866788132</v>
+        <v>0.1963716147065549</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.03345096192055744</v>
       </c>
       <c r="E41">
-        <v>-21.44582786285159</v>
+        <v>-23.93798723758291</v>
       </c>
       <c r="F41">
-        <v>-0.2667990636063669</v>
+        <v>-0.4222430351090969</v>
       </c>
       <c r="G41">
-        <v>-1.461957685101057</v>
+        <v>-0.4831790949143222</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.08960417222872397</v>
       </c>
       <c r="E42">
-        <v>-22.00303515382456</v>
+        <v>-23.40974859560061</v>
       </c>
       <c r="F42">
-        <v>-0.02487519198617411</v>
+        <v>-0.5227505088255666</v>
       </c>
       <c r="G42">
-        <v>-1.389151850688681</v>
+        <v>-0.01565217502693722</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.1822090181369444</v>
       </c>
       <c r="E43">
-        <v>-20.63707302156773</v>
+        <v>-22.80713839842462</v>
       </c>
       <c r="F43">
-        <v>-0.6745579474300067</v>
+        <v>-0.7551912304185107</v>
       </c>
       <c r="G43">
-        <v>-1.688298798172215</v>
+        <v>-0.1047621094108159</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.3177642659743537</v>
       </c>
       <c r="E44">
-        <v>-19.6181241551343</v>
+        <v>-21.96509141516093</v>
       </c>
       <c r="F44">
-        <v>-0.2328898439727692</v>
+        <v>-0.4014708941164966</v>
       </c>
       <c r="G44">
-        <v>-1.622957082545831</v>
+        <v>-0.2180475387084036</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.5022031876541203</v>
       </c>
       <c r="E45">
-        <v>-18.74977903776179</v>
+        <v>-21.4577226600859</v>
       </c>
       <c r="F45">
-        <v>-0.3746698951663213</v>
+        <v>-0.4567064325351676</v>
       </c>
       <c r="G45">
-        <v>-1.459328665297806</v>
+        <v>-0.1976967846206755</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.7363387021352034</v>
       </c>
       <c r="E46">
-        <v>-17.65394177007181</v>
+        <v>-20.13423542004809</v>
       </c>
       <c r="F46">
-        <v>-0.2072676118367776</v>
+        <v>-0.1529010308236433</v>
       </c>
       <c r="G46">
-        <v>-1.316604479990825</v>
+        <v>-0.325012355350906</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.026455999957779</v>
       </c>
       <c r="E47">
-        <v>-17.62319969984543</v>
+        <v>-19.07360077154735</v>
       </c>
       <c r="F47">
-        <v>-0.7626854703116378</v>
+        <v>-0.4456212199509046</v>
       </c>
       <c r="G47">
-        <v>-1.606864452886209</v>
+        <v>-0.71528995353184</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.371968058895541</v>
       </c>
       <c r="E48">
-        <v>-16.81911306809067</v>
+        <v>-18.44477550448903</v>
       </c>
       <c r="F48">
-        <v>0.1790141903344794</v>
+        <v>-0.4203659545743533</v>
       </c>
       <c r="G48">
-        <v>-2.943255004929869</v>
+        <v>-1.156367419966656</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.773189954404872</v>
       </c>
       <c r="E49">
-        <v>-16.52129043719854</v>
+        <v>-18.05713137227484</v>
       </c>
       <c r="F49">
-        <v>-0.3844454588867583</v>
+        <v>-0.2316224418464859</v>
       </c>
       <c r="G49">
-        <v>-1.834779844945808</v>
+        <v>-0.6331611501845983</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.230188933530402</v>
       </c>
       <c r="E50">
-        <v>-15.80460398456348</v>
+        <v>-17.47186498559132</v>
       </c>
       <c r="F50">
-        <v>-0.5831285520808169</v>
+        <v>-0.2668139742196173</v>
       </c>
       <c r="G50">
-        <v>-2.187971816209978</v>
+        <v>-1.335788231246326</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.735230028118272</v>
       </c>
       <c r="E51">
-        <v>-15.23671878727438</v>
+        <v>-16.74778581679807</v>
       </c>
       <c r="F51">
-        <v>-0.6279556540833122</v>
+        <v>-0.07807294659395836</v>
       </c>
       <c r="G51">
-        <v>-2.258592457399592</v>
+        <v>-0.6116512254984159</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.291209354690084</v>
       </c>
       <c r="E52">
-        <v>-14.93642499564397</v>
+        <v>-16.07514417026281</v>
       </c>
       <c r="F52">
-        <v>-0.8136905364042117</v>
+        <v>0.04534219927952879</v>
       </c>
       <c r="G52">
-        <v>-2.135174728343894</v>
+        <v>-1.549589938046366</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.892287001782802</v>
       </c>
       <c r="E53">
-        <v>-14.10125157712288</v>
+        <v>-15.17606528908658</v>
       </c>
       <c r="F53">
-        <v>-0.2533952506616681</v>
+        <v>0.00306232704064202</v>
       </c>
       <c r="G53">
-        <v>-1.892785368271163</v>
+        <v>-1.69877049472717</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.535431917695517</v>
       </c>
       <c r="E54">
-        <v>-13.81305193687037</v>
+        <v>-14.55494422903582</v>
       </c>
       <c r="F54">
-        <v>-0.1503007855462556</v>
+        <v>-0.04177720047289522</v>
       </c>
       <c r="G54">
-        <v>-2.12625381407606</v>
+        <v>-2.088672145686984</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.220931619424573</v>
       </c>
       <c r="E55">
-        <v>-13.25444086046961</v>
+        <v>-14.95012643980458</v>
       </c>
       <c r="F55">
-        <v>-0.6233217668320518</v>
+        <v>-0.1263518555639191</v>
       </c>
       <c r="G55">
-        <v>-2.805159669782932</v>
+        <v>-2.431395031140789</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.938387562930715</v>
       </c>
       <c r="E56">
-        <v>-12.85961167266346</v>
+        <v>-14.29754480396825</v>
       </c>
       <c r="F56">
-        <v>-0.03824007166294133</v>
+        <v>0.1233785504602562</v>
       </c>
       <c r="G56">
-        <v>-2.57034146902443</v>
+        <v>-2.189979478800544</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.691860939706999</v>
       </c>
       <c r="E57">
-        <v>-12.18736042799274</v>
+        <v>-13.38731039717352</v>
       </c>
       <c r="F57">
-        <v>0.4983846155446064</v>
+        <v>0.07177705983766661</v>
       </c>
       <c r="G57">
-        <v>-2.054883889188796</v>
+        <v>-2.9215649388669</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.473452685494475</v>
       </c>
       <c r="E58">
-        <v>-11.54356283410842</v>
+        <v>-12.92793199895689</v>
       </c>
       <c r="F58">
-        <v>-0.2273671184983048</v>
+        <v>0.4133195669511252</v>
       </c>
       <c r="G58">
-        <v>-4.147638478213068</v>
+        <v>-2.66801464566716</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.276970203503055</v>
       </c>
       <c r="E59">
-        <v>-11.81027375896625</v>
+        <v>-12.15256897672465</v>
       </c>
       <c r="F59">
-        <v>-0.06659674459557401</v>
+        <v>0.09680286744364247</v>
       </c>
       <c r="G59">
-        <v>-4.392450609266351</v>
+        <v>-3.569755384459324</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.100308831326423</v>
       </c>
       <c r="E60">
-        <v>-10.31913383737909</v>
+        <v>-11.82895905671666</v>
       </c>
       <c r="F60">
-        <v>-0.7079005637600897</v>
+        <v>0.00860990353719031</v>
       </c>
       <c r="G60">
-        <v>-3.46349024736724</v>
+        <v>-3.263240915739669</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.923873056358278</v>
       </c>
       <c r="E61">
-        <v>-11.00826788608524</v>
+        <v>-11.52185399851354</v>
       </c>
       <c r="F61">
-        <v>-0.3383236186336874</v>
+        <v>-0.06438997383451613</v>
       </c>
       <c r="G61">
-        <v>-4.687391647213602</v>
+        <v>-3.796715243998575</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.74301663275531</v>
       </c>
       <c r="E62">
-        <v>-10.12287798943564</v>
+        <v>-11.12219877914793</v>
       </c>
       <c r="F62">
-        <v>-0.2716847745480784</v>
+        <v>-0.1834528773736947</v>
       </c>
       <c r="G62">
-        <v>-3.701783349176514</v>
+        <v>-3.773610154367223</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.53834313591517</v>
       </c>
       <c r="E63">
-        <v>-8.567421437272181</v>
+        <v>-10.47857146692793</v>
       </c>
       <c r="F63">
-        <v>-0.09778726241318379</v>
+        <v>-0.1454125895023358</v>
       </c>
       <c r="G63">
-        <v>-3.703952877931729</v>
+        <v>-4.496068451343047</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.29172597184694</v>
       </c>
       <c r="E64">
-        <v>-9.05198075575125</v>
+        <v>-10.37077071378068</v>
       </c>
       <c r="F64">
-        <v>-0.8544967430335182</v>
+        <v>-0.3430096930313242</v>
       </c>
       <c r="G64">
-        <v>-4.354589591206027</v>
+        <v>-4.779532656067763</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.99484746233961</v>
       </c>
       <c r="E65">
-        <v>-9.944809053883617</v>
+        <v>-9.672017827646229</v>
       </c>
       <c r="F65">
-        <v>-0.6839135288772243</v>
+        <v>-0.2920311346956398</v>
       </c>
       <c r="G65">
-        <v>-4.040070579570018</v>
+        <v>-4.953878179862309</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.62208100544895</v>
       </c>
       <c r="E66">
-        <v>-9.785147150923233</v>
+        <v>-9.615314033428344</v>
       </c>
       <c r="F66">
-        <v>-0.530499885878756</v>
+        <v>-0.02430610358045085</v>
       </c>
       <c r="G66">
-        <v>-5.2805058249119</v>
+        <v>-4.828815681714208</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.16904888646415</v>
       </c>
       <c r="E67">
-        <v>-9.391655297163679</v>
+        <v>-9.656106875060811</v>
       </c>
       <c r="F67">
-        <v>-0.9860124937389817</v>
+        <v>-0.3768203369439889</v>
       </c>
       <c r="G67">
-        <v>-4.54269634974033</v>
+        <v>-5.068385437628537</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.61997903693901</v>
       </c>
       <c r="E68">
-        <v>-9.056727876295531</v>
+        <v>-9.208432226357543</v>
       </c>
       <c r="F68">
-        <v>-0.7003872714166981</v>
+        <v>-0.2521311620049961</v>
       </c>
       <c r="G68">
-        <v>-4.330247008638486</v>
+        <v>-4.869872251154056</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.96043555344772</v>
       </c>
       <c r="E69">
-        <v>-8.979648427318036</v>
+        <v>-9.518859853620526</v>
       </c>
       <c r="F69">
-        <v>-1.163317909368993</v>
+        <v>-0.5620093251464435</v>
       </c>
       <c r="G69">
-        <v>-4.517009233708366</v>
+        <v>-4.776825313926778</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.19291997760132</v>
       </c>
       <c r="E70">
-        <v>-8.130682193987186</v>
+        <v>-9.049085967457845</v>
       </c>
       <c r="F70">
-        <v>-0.5436278524783225</v>
+        <v>-0.6535604905038449</v>
       </c>
       <c r="G70">
-        <v>-5.007296624941077</v>
+        <v>-4.198803850709706</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.30454075082469</v>
       </c>
       <c r="E71">
-        <v>-8.009578704966509</v>
+        <v>-8.796952814350155</v>
       </c>
       <c r="F71">
-        <v>-0.7638990285567391</v>
+        <v>-0.8347749719076676</v>
       </c>
       <c r="G71">
-        <v>-5.748455685423045</v>
+        <v>-4.788106341304979</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.30621543566488</v>
       </c>
       <c r="E72">
-        <v>-8.337105103253814</v>
+        <v>-9.229318726110105</v>
       </c>
       <c r="F72">
-        <v>-0.7940590573252663</v>
+        <v>-0.8268905709678218</v>
       </c>
       <c r="G72">
-        <v>-4.3948159438659</v>
+        <v>-4.499219620064521</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.20128661656182</v>
       </c>
       <c r="E73">
-        <v>-8.941438883129614</v>
+        <v>-8.869509416194909</v>
       </c>
       <c r="F73">
-        <v>-1.002654394861224</v>
+        <v>-0.5185506860933731</v>
       </c>
       <c r="G73">
-        <v>-4.00072404783735</v>
+        <v>-4.433661212637075</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.99160313246318</v>
       </c>
       <c r="E74">
-        <v>-10.34022384448657</v>
+        <v>-9.128034361531512</v>
       </c>
       <c r="F74">
-        <v>-0.8688341260411721</v>
+        <v>-0.6576020950621037</v>
       </c>
       <c r="G74">
-        <v>-3.45387487503817</v>
+        <v>-4.47588478490915</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.69619369974772</v>
       </c>
       <c r="E75">
-        <v>-7.526016157205397</v>
+        <v>-9.621527237570287</v>
       </c>
       <c r="F75">
-        <v>-1.075920178169229</v>
+        <v>-1.110588182343791</v>
       </c>
       <c r="G75">
-        <v>-4.001415895153995</v>
+        <v>-4.53718506790849</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.3140438619473</v>
       </c>
       <c r="E76">
-        <v>-7.65081600430517</v>
+        <v>-9.690968930921422</v>
       </c>
       <c r="F76">
-        <v>-1.380688142802806</v>
+        <v>-0.7744814221275027</v>
       </c>
       <c r="G76">
-        <v>-3.673548146423624</v>
+        <v>-3.939131361443805</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.86291101088925</v>
       </c>
       <c r="E77">
-        <v>-9.682479766973472</v>
+        <v>-9.730536575213064</v>
       </c>
       <c r="F77">
-        <v>-1.07929080513122</v>
+        <v>-0.946339493716705</v>
       </c>
       <c r="G77">
-        <v>-3.269321339892372</v>
+        <v>-3.520772594440857</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.35199807658257</v>
       </c>
       <c r="E78">
-        <v>-9.547176448433207</v>
+        <v>-10.3225643899334</v>
       </c>
       <c r="F78">
-        <v>-1.619800535457897</v>
+        <v>-0.8341379573749147</v>
       </c>
       <c r="G78">
-        <v>-3.139233158406379</v>
+        <v>-3.662854536578424</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.78357679786412</v>
       </c>
       <c r="E79">
-        <v>-10.13883462734563</v>
+        <v>-10.40627651739664</v>
       </c>
       <c r="F79">
-        <v>-1.583295212383926</v>
+        <v>-0.8517689291760994</v>
       </c>
       <c r="G79">
-        <v>-3.052647814042107</v>
+        <v>-3.086475231709162</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.17622692344383</v>
       </c>
       <c r="E80">
-        <v>-12.21283207304791</v>
+        <v>-11.63404054281981</v>
       </c>
       <c r="F80">
-        <v>-0.9094348975545842</v>
+        <v>-1.078104583010411</v>
       </c>
       <c r="G80">
-        <v>-3.246730566945469</v>
+        <v>-2.624451761419844</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.52740448379702</v>
       </c>
       <c r="E81">
-        <v>-11.88629829226724</v>
+        <v>-11.77046522841777</v>
       </c>
       <c r="F81">
-        <v>-0.8893262788516262</v>
+        <v>-1.18513047981951</v>
       </c>
       <c r="G81">
-        <v>-2.057633003243238</v>
+        <v>-2.299079884518577</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.84840404042071</v>
       </c>
       <c r="E82">
-        <v>-13.58717123254692</v>
+        <v>-12.30271171932852</v>
       </c>
       <c r="F82">
-        <v>-1.811744859830182</v>
+        <v>-1.14616076372221</v>
       </c>
       <c r="G82">
-        <v>-2.544677849693786</v>
+        <v>-2.086640986395098</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.14378505761732</v>
       </c>
       <c r="E83">
-        <v>-13.30791345627678</v>
+        <v>-13.39397630134987</v>
       </c>
       <c r="F83">
-        <v>-1.350314395244357</v>
+        <v>-1.449689490721199</v>
       </c>
       <c r="G83">
-        <v>-1.716191993383669</v>
+        <v>-1.460913387264612</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.408891185669336</v>
       </c>
       <c r="E84">
-        <v>-14.04000416971563</v>
+        <v>-14.59075321707849</v>
       </c>
       <c r="F84">
-        <v>-1.292915989536976</v>
+        <v>-1.397471694750927</v>
       </c>
       <c r="G84">
-        <v>-2.308820572588021</v>
+        <v>-1.994899421463377</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.65759532156286</v>
       </c>
       <c r="E85">
-        <v>-14.62093875698735</v>
+        <v>-15.2942989090818</v>
       </c>
       <c r="F85">
-        <v>-1.749527840940717</v>
+        <v>-1.346536211520188</v>
       </c>
       <c r="G85">
-        <v>-2.083126924175459</v>
+        <v>-1.460466949939532</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.890664220332348</v>
       </c>
       <c r="E86">
-        <v>-16.85788329580795</v>
+        <v>-16.46141358952849</v>
       </c>
       <c r="F86">
-        <v>-1.684341953279618</v>
+        <v>-1.515982905599841</v>
       </c>
       <c r="G86">
-        <v>-1.222372264719182</v>
+        <v>-1.002701604078319</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.124511922840319</v>
       </c>
       <c r="E87">
-        <v>-16.66977189527249</v>
+        <v>-17.8611787087581</v>
       </c>
       <c r="F87">
-        <v>-1.607715483418455</v>
+        <v>-1.666510516566956</v>
       </c>
       <c r="G87">
-        <v>-1.511692369561766</v>
+        <v>-0.8702637524603246</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.376971348963426</v>
       </c>
       <c r="E88">
-        <v>-18.680661294894</v>
+        <v>-19.65541168640861</v>
       </c>
       <c r="F88">
-        <v>-2.131374564037385</v>
+        <v>-1.811749830034599</v>
       </c>
       <c r="G88">
-        <v>-1.344805743064031</v>
+        <v>-0.7566284833875278</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.658381071958982</v>
       </c>
       <c r="E89">
-        <v>-19.90348715205194</v>
+        <v>-19.80482346381931</v>
       </c>
       <c r="F89">
-        <v>-2.386076831213163</v>
+        <v>-1.67584124699209</v>
       </c>
       <c r="G89">
-        <v>-0.8976687384332408</v>
+        <v>-0.4135975300719709</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.996278876080867</v>
       </c>
       <c r="E90">
-        <v>-22.43328292780885</v>
+        <v>-21.79849364928808</v>
       </c>
       <c r="F90">
-        <v>-2.390231093738203</v>
+        <v>-2.046787483435319</v>
       </c>
       <c r="G90">
-        <v>-1.151702019382337</v>
+        <v>-0.6477108297908726</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.403482392251354</v>
       </c>
       <c r="E91">
-        <v>-23.20151903940769</v>
+        <v>-22.99286585565963</v>
       </c>
       <c r="F91">
-        <v>-1.719176459302143</v>
+        <v>-1.830114735354664</v>
       </c>
       <c r="G91">
-        <v>-0.5342452591164981</v>
+        <v>-0.3290694524454961</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.900935971107049</v>
       </c>
       <c r="E92">
-        <v>-26.66560462195273</v>
+        <v>-25.34997941095282</v>
       </c>
       <c r="F92">
-        <v>-2.118925030340712</v>
+        <v>-2.228566911407851</v>
       </c>
       <c r="G92">
-        <v>-0.7414835540144796</v>
+        <v>-0.5615875872192275</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.507797955329589</v>
       </c>
       <c r="E93">
-        <v>-26.85503259047816</v>
+        <v>-27.58341863941526</v>
       </c>
       <c r="F93">
-        <v>-2.210785176739357</v>
+        <v>-2.281634612333396</v>
       </c>
       <c r="G93">
-        <v>-0.6848330071319124</v>
+        <v>-0.3237095937999405</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.228967539685489</v>
       </c>
       <c r="E94">
-        <v>-30.01542290131776</v>
+        <v>-29.42204113970553</v>
       </c>
       <c r="F94">
-        <v>-2.276887238747952</v>
+        <v>-2.459466869631588</v>
       </c>
       <c r="G94">
-        <v>-1.273023320531371</v>
+        <v>0.07012122776949867</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.077878567554042</v>
       </c>
       <c r="E95">
-        <v>-32.36863036135995</v>
+        <v>-31.82770988859729</v>
       </c>
       <c r="F95">
-        <v>-2.31066640469931</v>
+        <v>-2.629979672558644</v>
       </c>
       <c r="G95">
-        <v>-1.055532631624088</v>
+        <v>-0.1098321754067579</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.049958948471464</v>
       </c>
       <c r="E96">
-        <v>-33.56824392042343</v>
+        <v>-33.43912888675715</v>
       </c>
       <c r="F96">
-        <v>-3.166438686285632</v>
+        <v>-2.806513049769247</v>
       </c>
       <c r="G96">
-        <v>-1.025584780419427</v>
+        <v>-0.01275163778621037</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.134256905601501</v>
       </c>
       <c r="E97">
-        <v>-36.80913384976652</v>
+        <v>-36.16463020995698</v>
       </c>
       <c r="F97">
-        <v>-2.797355448131298</v>
+        <v>-2.785231462823925</v>
       </c>
       <c r="G97">
-        <v>-1.525145536439772</v>
+        <v>-0.3468460123663864</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.320261992570361</v>
       </c>
       <c r="E98">
-        <v>-38.67616431551862</v>
+        <v>-37.91669563302649</v>
       </c>
       <c r="F98">
-        <v>-3.300360015928825</v>
+        <v>-3.291860966376102</v>
       </c>
       <c r="G98">
-        <v>-1.552145857001066</v>
+        <v>-0.3771149851557539</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.568431888538905</v>
       </c>
       <c r="E99">
-        <v>-41.72692646022804</v>
+        <v>-40.69573600341468</v>
       </c>
       <c r="F99">
-        <v>-3.56120131392675</v>
+        <v>-3.23653927774754</v>
       </c>
       <c r="G99">
-        <v>-1.543822803244597</v>
+        <v>-0.6464576723871382</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.865516135526684</v>
       </c>
       <c r="E100">
-        <v>-42.88751644568343</v>
+        <v>-42.96269580047981</v>
       </c>
       <c r="F100">
-        <v>-3.090807085675232</v>
+        <v>-3.298336314363786</v>
       </c>
       <c r="G100">
-        <v>-1.37601719465079</v>
+        <v>-0.8118222347882538</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.15378068710067</v>
       </c>
       <c r="E101">
-        <v>-45.72131379248099</v>
+        <v>-44.97739161828053</v>
       </c>
       <c r="F101">
-        <v>-3.807012713768281</v>
+        <v>-3.76919359999347</v>
       </c>
       <c r="G101">
-        <v>-2.420657038637541</v>
+        <v>-1.008701095148698</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.433121129661405</v>
       </c>
       <c r="E102">
-        <v>-47.62842586242618</v>
+        <v>-47.74351446314567</v>
       </c>
       <c r="F102">
-        <v>-3.666442907350219</v>
+        <v>-3.811181886906571</v>
       </c>
       <c r="G102">
-        <v>-2.841336757581989</v>
+        <v>-1.355389701636404</v>
       </c>
     </row>
   </sheetData>
